--- a/AAAGameData/DataTables/SceneTable.xlsx
+++ b/AAAGameData/DataTables/SceneTable.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -733,6 +733,41 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>StartGame</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>scene.menu.name</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>scene.menu.desc</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1" t="n"/>
+      <c r="J8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/AAAGameData/DataTables/SceneTable.xlsx
+++ b/AAAGameData/DataTables/SceneTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="11855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -153,14 +153,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -616,148 +609,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1113,7 +1106,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1211,7 +1204,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:11">
+    <row r="4" ht="27" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>

--- a/AAAGameData/DataTables/SceneTable.xlsx
+++ b/AAAGameData/DataTables/SceneTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t>#</t>
   </si>
@@ -68,6 +68,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>int[]</t>
+  </si>
+  <si>
     <t>场景ID</t>
   </si>
   <si>
@@ -107,9 +110,6 @@
     <t>scene.base.desc</t>
   </si>
   <si>
-    <t>1001</t>
-  </si>
-  <si>
     <t>WorldScene</t>
   </si>
   <si>
@@ -119,9 +119,6 @@
     <t>scene.world.desc</t>
   </si>
   <si>
-    <t>2001</t>
-  </si>
-  <si>
     <t>TutorialScene</t>
   </si>
   <si>
@@ -129,9 +126,6 @@
   </si>
   <si>
     <t>scene.tutorial.desc</t>
-  </si>
-  <si>
-    <t>3001</t>
   </si>
   <si>
     <t>StartGame</t>
@@ -1195,7 +1189,7 @@
         <v>11</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>11</v>
@@ -1209,34 +1203,34 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:11">
@@ -1246,23 +1240,21 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="I5" s="1"/>
       <c r="J5" s="1">
         <v>1</v>
       </c>
@@ -1291,9 +1283,7 @@
       <c r="H6" s="1">
         <v>1</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="I6" s="1"/>
       <c r="J6" s="1">
         <v>1</v>
       </c>
@@ -1308,23 +1298,21 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="I7" s="1"/>
       <c r="J7" s="1">
         <v>1</v>
       </c>
@@ -1339,16 +1327,16 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>

--- a/AAAGameData/DataTables/SceneTable.xlsx
+++ b/AAAGameData/DataTables/SceneTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>

--- a/AAAGameData/DataTables/SceneTable.xlsx
+++ b/AAAGameData/DataTables/SceneTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>

--- a/AAAGameData/DataTables/SceneTable.xlsx
+++ b/AAAGameData/DataTables/SceneTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
   <si>
     <t>#</t>
   </si>
@@ -135,6 +135,87 @@
   </si>
   <si>
     <t>scene.menu.desc</t>
+  </si>
+  <si>
+    <t>TiangongScene</t>
+  </si>
+  <si>
+    <t>scene.tiangong.name</t>
+  </si>
+  <si>
+    <t>scene.tiangong.desc</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>HerheimScene</t>
+  </si>
+  <si>
+    <t>scene.herheim.name</t>
+  </si>
+  <si>
+    <t>scene.herheim.desc</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>TakamaharaScene</t>
+  </si>
+  <si>
+    <t>scene.takamahara.name</t>
+  </si>
+  <si>
+    <t>scene.takamahara.desc</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>OlympusScene</t>
+  </si>
+  <si>
+    <t>scene.olympus.name</t>
+  </si>
+  <si>
+    <t>scene.olympus.desc</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>BabylonScene</t>
+  </si>
+  <si>
+    <t>scene.babylon.name</t>
+  </si>
+  <si>
+    <t>scene.babylon.desc</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>AvalonScene</t>
+  </si>
+  <si>
+    <t>scene.avalon.name</t>
+  </si>
+  <si>
+    <t>scene.avalon.desc</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>AbyssScene</t>
+  </si>
+  <si>
+    <t>scene.abyss.name</t>
+  </si>
+  <si>
+    <t>scene.abyss.desc</t>
   </si>
 </sst>
 </file>
@@ -147,7 +228,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -603,154 +691,157 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1099,8 +1190,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1128,7 +1219,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="I1" s="2"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
@@ -1155,7 +1246,7 @@
       <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J2" s="1" t="s">
@@ -1188,7 +1279,7 @@
       <c r="H3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="J3" s="1" t="s">
@@ -1198,7 +1289,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:11">
+    <row r="4" ht="28.8" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1223,7 +1314,7 @@
       <c r="H4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -1254,7 +1345,7 @@
       <c r="H5" s="1">
         <v>1</v>
       </c>
-      <c r="I5" s="1"/>
+      <c r="I5" s="2"/>
       <c r="J5" s="1">
         <v>1</v>
       </c>
@@ -1283,7 +1374,7 @@
       <c r="H6" s="1">
         <v>1</v>
       </c>
-      <c r="I6" s="1"/>
+      <c r="I6" s="2"/>
       <c r="J6" s="1">
         <v>1</v>
       </c>
@@ -1312,7 +1403,7 @@
       <c r="H7" s="1">
         <v>0</v>
       </c>
-      <c r="I7" s="1"/>
+      <c r="I7" s="2"/>
       <c r="J7" s="1">
         <v>1</v>
       </c>
@@ -1341,12 +1432,227 @@
       <c r="H8" s="1">
         <v>0</v>
       </c>
-      <c r="I8" s="1"/>
+      <c r="I8" s="2"/>
       <c r="J8" s="1">
         <v>0</v>
       </c>
       <c r="K8" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:11">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="1">
+        <v>4</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="1">
+        <v>3</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:11">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1">
+        <v>11</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="1">
+        <v>3</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" s="1">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:11">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="1">
+        <v>4</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="1">
+        <v>3</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:11">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1">
+        <v>13</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="1">
+        <v>4</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="1">
+        <v>3</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:11">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1">
+        <v>14</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="1">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="1">
+        <v>3</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:11">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1">
+        <v>15</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="1">
+        <v>4</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="1">
+        <v>3</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:11">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1">
+        <v>16</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="1">
+        <v>4</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="1">
+        <v>99</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="1">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/SceneTable.xlsx
+++ b/AAAGameData/DataTables/SceneTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
   <si>
     <t>#</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>BaseScene</t>
+  </si>
+  <si>
+    <t>BaseRoom</t>
   </si>
   <si>
     <t>scene.base.name</t>
@@ -228,14 +231,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -691,148 +687,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1191,7 +1187,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1289,7 +1285,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:11">
+    <row r="4" ht="27" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1329,18 +1325,20 @@
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="D5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
@@ -1360,16 +1358,16 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -1389,16 +1387,16 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -1418,16 +1416,16 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
@@ -1447,22 +1445,22 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H9" s="1">
         <v>3</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J9" s="1">
         <v>1</v>
@@ -1478,22 +1476,22 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H10" s="1">
         <v>3</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J10" s="1">
         <v>1</v>
@@ -1509,22 +1507,22 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H11" s="1">
         <v>3</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J11" s="1">
         <v>1</v>
@@ -1540,22 +1538,22 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H12" s="1">
         <v>3</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J12" s="1">
         <v>1</v>
@@ -1571,22 +1569,22 @@
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H13" s="1">
         <v>3</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J13" s="1">
         <v>1</v>
@@ -1602,22 +1600,22 @@
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H14" s="1">
         <v>3</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J14" s="1">
         <v>1</v>
@@ -1633,16 +1631,16 @@
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E15" s="1">
         <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H15" s="1">
         <v>99</v>

--- a/AAAGameData/DataTables/SceneTable.xlsx
+++ b/AAAGameData/DataTables/SceneTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1187,7 +1187,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1285,7 +1285,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:11">
+    <row r="4" ht="28.8" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>40</v>
       </c>
       <c r="J9" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>

--- a/AAAGameData/DataTables/SceneTable.xlsx
+++ b/AAAGameData/DataTables/SceneTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="15300"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1187,7 +1187,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1285,7 +1285,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:11">
+    <row r="4" ht="27" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>

--- a/AAAGameData/DataTables/SceneTable.xlsx
+++ b/AAAGameData/DataTables/SceneTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="67">
   <si>
     <t>#</t>
   </si>
@@ -219,6 +219,15 @@
   </si>
   <si>
     <t>scene.abyss.desc</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>test.name</t>
+  </si>
+  <si>
+    <t>test.desc</t>
   </si>
 </sst>
 </file>
@@ -1186,7 +1195,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1653,6 +1662,32 @@
         <v>30</v>
       </c>
     </row>
+    <row r="16" spans="1:11">
+      <c r="B16">
+        <v>99</v>
+      </c>
+      <c r="D16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
